--- a/examples/demos/07_insurance_aggregate.xlsx
+++ b/examples/demos/07_insurance_aggregate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1676F650-85BE-45E2-9B94-D9700178A59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25201AE5-171F-463A-B877-321F90E1A08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -467,14 +467,14 @@
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -793,22 +793,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="22"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="18"/>
+      <c r="B4" s="20"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="10" t="s">
@@ -826,10 +826,10 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="18"/>
+      <c r="B9" s="20"/>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="10" t="s">
@@ -852,10 +852,10 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="18"/>
+      <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="10" t="s">
@@ -873,10 +873,10 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="18"/>
+      <c r="B20" s="20"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="13">
@@ -987,10 +987,10 @@
       </c>
     </row>
     <row r="45" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B45" s="18"/>
+      <c r="B45" s="20"/>
     </row>
     <row r="46" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B46" s="10" t="s">
@@ -1008,10 +1008,10 @@
       </c>
     </row>
     <row r="50" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="18"/>
+      <c r="B50" s="20"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51" s="14"/>
@@ -1071,25 +1071,25 @@
       <c r="A1" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
@@ -5194,37 +5194,37 @@
       <c r="A1" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
@@ -5257,13 +5257,13 @@
       <c r="A12" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">

--- a/examples/demos/07_insurance_aggregate.xlsx
+++ b/examples/demos/07_insurance_aggregate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25201AE5-171F-463A-B877-321F90E1A08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BD17E8-7F50-4738-BE83-87E760F98352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
